--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486267_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486267_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6152</v>
+        <v>5.6696</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3402</v>
+        <v>3.8261</v>
       </c>
       <c r="F2" t="n">
-        <v>2.275</v>
+        <v>1.8435</v>
       </c>
       <c r="G2" t="n">
         <v>-0.7204</v>
@@ -610,13 +610,13 @@
         <v>2.6101</v>
       </c>
       <c r="S2" t="n">
-        <v>5.7256</v>
+        <v>3.7799</v>
       </c>
       <c r="T2" t="n">
-        <v>4.8405</v>
+        <v>3.3263</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8852</v>
+        <v>0.4536</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3226</v>
+        <v>4.4414</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3679</v>
+        <v>4.4558</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0453</v>
+        <v>-0.0145</v>
       </c>
       <c r="G3" t="n">
         <v>1.3833</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8518</v>
+        <v>1.9705</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7867</v>
+        <v>1.8747</v>
       </c>
       <c r="U3" t="n">
-        <v>0.065</v>
+        <v>0.0958</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8116</v>
+        <v>3.2164</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1899</v>
+        <v>3.6564</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3783</v>
+        <v>-0.44</v>
       </c>
       <c r="G4" t="n">
         <v>0.504</v>
@@ -766,13 +766,13 @@
         <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4801</v>
+        <v>1.8849</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3758</v>
+        <v>1.8422</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1043</v>
+        <v>0.0427</v>
       </c>
       <c r="V4" t="n">
         <v>-1.13</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1718</v>
+        <v>0.2392</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7131999999999999</v>
+        <v>0.4716</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5414</v>
+        <v>-0.2324</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0903</v>
+        <v>-0.9853</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6878</v>
+        <v>-0.1279</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4024</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4719</v>
+        <v>-0.5956</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4719</v>
+        <v>0.073</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.6686</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.3898</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.216</v>
+        <v>-0.2009</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4024</v>
+        <v>-0.1889</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9146</v>
+        <v>0.572</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0551</v>
+        <v>1.0671</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1405</v>
+        <v>-0.4951</v>
       </c>
       <c r="V5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5737</v>
+        <v>0.1769</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9931</v>
+        <v>-0.3658</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4194</v>
+        <v>0.5427</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4547</v>
@@ -922,13 +922,13 @@
         <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2038</v>
+        <v>0.5468</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1406</v>
+        <v>0.7679</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3444</v>
+        <v>-0.2211</v>
       </c>
       <c r="V6" t="n">
         <v>2.2599</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>J. LOBO MARTORELL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6549</v>
+        <v>0.0621</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4225</v>
+        <v>-0.9343</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2324</v>
+        <v>0.9964</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9853</v>
+        <v>-1.1723</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1279</v>
+        <v>-0.6966</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.4757</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5956</v>
+        <v>-0.4152</v>
       </c>
       <c r="K7" t="n">
-        <v>0.073</v>
+        <v>-0.3618</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6686</v>
+        <v>-0.0533</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3898</v>
+        <v>-0.7572</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2009</v>
+        <v>-0.3348</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1889</v>
+        <v>-0.4224</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6525</v>
+        <v>1.9576</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3221</v>
+        <v>1.6695</v>
       </c>
       <c r="T7" t="n">
-        <v>0.173</v>
+        <v>1.8735</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4951</v>
+        <v>-0.204</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9902</v>
+        <v>-0.2444</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8996</v>
+        <v>0.2662</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9094</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.8592</v>
+        <v>-2.0903</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.9182</v>
+        <v>-1.6878</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-0.4024</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.3386</v>
+        <v>-1.4719</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.5219</v>
+        <v>-1.4719</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8167</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5206</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3963</v>
+        <v>-0.216</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1243</v>
+        <v>-0.4024</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1751</v>
+        <v>0.2175</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3926</v>
+        <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3688</v>
+        <v>0.4984</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3313</v>
+        <v>0.6081</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0375</v>
+        <v>-0.1097</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LOBO MARTORELL</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3282</v>
+        <v>-0.6978</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2321</v>
+        <v>-1.6689</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9039</v>
+        <v>0.9711</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1723</v>
+        <v>-6.8592</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6966</v>
+        <v>-5.9182</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4757</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4152</v>
+        <v>-5.3386</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3618</v>
+        <v>-4.5219</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0533</v>
+        <v>-0.8167</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7572</v>
+        <v>-1.5206</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3348</v>
+        <v>-1.3963</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4224</v>
+        <v>-0.1243</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9576</v>
+        <v>2.3926</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2792</v>
+        <v>2.6612</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5756</v>
+        <v>2.562</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2965</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0167</v>
+        <v>-1.3458</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1573</v>
+        <v>-1.5481</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1407</v>
+        <v>0.2023</v>
       </c>
       <c r="G10" t="n">
         <v>-3.3342</v>
@@ -1234,13 +1234,13 @@
         <v>2.8276</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1202</v>
+        <v>1.7911</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9661999999999999</v>
+        <v>1.5754</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1541</v>
+        <v>0.2157</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3252</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2541</v>
+        <v>-2.0053</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7591</v>
+        <v>-2.5103</v>
       </c>
       <c r="F11" t="n">
         <v>0.505</v>
@@ -1312,10 +1312,10 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>0.161</v>
+        <v>0.4098</v>
       </c>
       <c r="T11" t="n">
-        <v>0.161</v>
+        <v>0.4098</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.8538</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.023899999999999</v>
+        <v>-7.8126</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8298</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>0.4558</v>
@@ -1390,13 +1390,13 @@
         <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9557</v>
+        <v>2.2595</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7811</v>
+        <v>1.9924</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1746</v>
+        <v>0.2671</v>
       </c>
       <c r="V12" t="n">
         <v>-1.695</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7504000000000026</v>
+        <v>0.962299999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.876399999999999</v>
+        <v>-2.163899999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>3.126199999999999</v>
+        <v>3.1261</v>
       </c>
       <c r="G13" t="n">
         <v>-14.3833</v>
@@ -1441,13 +1441,13 @@
         <v>-0.5457000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.2662</v>
+        <v>-5.266199999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-6.186699999999999</v>
+        <v>-6.1867</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9205999999999999</v>
+        <v>0.9206</v>
       </c>
       <c r="M13" t="n">
         <v>-9.117599999999999</v>
@@ -1459,7 +1459,7 @@
         <v>-1.4663</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.2626</v>
+        <v>-3.262599999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-20.6631</v>
@@ -1468,13 +1468,13 @@
         <v>17.4005</v>
       </c>
       <c r="S13" t="n">
-        <v>16.3311</v>
+        <v>18.0436</v>
       </c>
       <c r="T13" t="n">
-        <v>16.1869</v>
+        <v>17.8994</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1441999999999999</v>
+        <v>0.1441000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0.5649</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.6745</v>
+        <v>7.7812</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6015</v>
+        <v>6.2662</v>
       </c>
       <c r="F14" t="n">
-        <v>1.073</v>
+        <v>1.515</v>
       </c>
       <c r="G14" t="n">
         <v>7.4183</v>
@@ -1546,13 +1546,13 @@
         <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.9389</v>
+        <v>-1.8323</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6682</v>
+        <v>0.3329</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.6071</v>
+        <v>-2.1652</v>
       </c>
       <c r="V14" t="n">
         <v>1.3252</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9102</v>
+        <v>6.1761</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7621</v>
+        <v>3.4268</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1481</v>
+        <v>2.7492</v>
       </c>
       <c r="G15" t="n">
         <v>4.7466</v>
@@ -1624,13 +1624,13 @@
         <v>3.0451</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2263</v>
+        <v>-0.9605</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6682</v>
+        <v>0.3329</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.8945</v>
+        <v>-1.2933</v>
       </c>
       <c r="V15" t="n">
         <v>2.8249</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ARAMBURU LAMY</t>
+          <t>B. VAZQUEZ ARRAIZA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1771</v>
+        <v>0.8754</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4119</v>
+        <v>-2.066</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7652</v>
+        <v>2.9414</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0627</v>
+        <v>4.1132</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4961</v>
+        <v>1.0978</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5665</v>
+        <v>3.0153</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8676</v>
+        <v>1.8518</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6054</v>
+        <v>0.2222</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2622</v>
+        <v>1.6296</v>
       </c>
       <c r="M16" t="n">
-        <v>0.195</v>
+        <v>2.2614</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8907</v>
+        <v>0.8757</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6957</v>
+        <v>1.3857</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.2626</v>
+        <v>-3.4801</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6101</v>
+        <v>3.0451</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4369</v>
+        <v>-1.4982</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4817</v>
+        <v>-0.2632</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.9187</v>
+        <v>-1.2351</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2039</v>
+        <v>-1.3045</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3252</v>
+        <v>-0.1745</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1213</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. VAZQUEZ ARRAIZA</t>
+          <t>J. ARAMBURU LAMY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5209</v>
+        <v>0.7526</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.6248</v>
+        <v>0.1826</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1039</v>
+        <v>0.57</v>
       </c>
       <c r="G17" t="n">
-        <v>4.1132</v>
+        <v>2.0627</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0978</v>
+        <v>1.4961</v>
       </c>
       <c r="I17" t="n">
-        <v>3.0153</v>
+        <v>0.5665</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8518</v>
+        <v>1.8676</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2222</v>
+        <v>0.6054</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6296</v>
+        <v>1.2622</v>
       </c>
       <c r="M17" t="n">
-        <v>2.2614</v>
+        <v>0.195</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8757</v>
+        <v>0.8907</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3857</v>
+        <v>-0.6957</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.435</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4801</v>
+        <v>-3.2626</v>
       </c>
       <c r="R17" t="n">
-        <v>3.0451</v>
+        <v>2.6101</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.8945</v>
+        <v>-1.8614</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.822</v>
+        <v>0.2524</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.0726</v>
+        <v>-2.1138</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.3045</v>
+        <v>1.2039</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.1745</v>
+        <v>1.3252</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>-0.1213</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1012</v>
+        <v>-1.4513</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1945</v>
+        <v>-0.971</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.4803</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6956</v>
@@ -1858,13 +1858,13 @@
         <v>2.3926</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.6547</v>
+        <v>-2.0047</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2139</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.4408</v>
+        <v>-2.0144</v>
       </c>
       <c r="V18" t="n">
         <v>0.074</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1824</v>
+        <v>-1.9318</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0835</v>
+        <v>-0.9718</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0988</v>
+        <v>-0.96</v>
       </c>
       <c r="G19" t="n">
         <v>1.4491</v>
@@ -1936,13 +1936,13 @@
         <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2415</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1286</v>
+        <v>0.2403</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3701</v>
+        <v>-0.2313</v>
       </c>
       <c r="V19" t="n">
         <v>-3.3899</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>J. BOCCA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0571</v>
+        <v>-1.9897</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7524</v>
+        <v>-2.9604</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3047</v>
+        <v>0.9707</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8962</v>
+        <v>-0.4327</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5718</v>
+        <v>1.2559</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3244</v>
+        <v>-1.6886</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.0674</v>
+        <v>-0.2987</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3989</v>
+        <v>0.3317</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6686</v>
+        <v>-0.6303</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1713</v>
+        <v>-0.134</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.9242</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6558</v>
+        <v>-1.0583</v>
       </c>
       <c r="P20" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>2.8276</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.5399</v>
+        <v>-2.0883</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.4867</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.8549</v>
+        <v>-1.6016</v>
       </c>
       <c r="V20" t="n">
-        <v>0.074</v>
+        <v>-0.1213</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.074</v>
+        <v>-0.1213</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BOCCA</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1368</v>
+        <v>-2.1887</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2957</v>
+        <v>-2.3053</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1589</v>
+        <v>0.1166</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4327</v>
+        <v>-1.8962</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2559</v>
+        <v>-0.5718</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6886</v>
+        <v>-1.3244</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2987</v>
+        <v>-2.0674</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3317</v>
+        <v>-1.3989</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6303</v>
+        <v>-0.6686</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.134</v>
+        <v>0.1713</v>
       </c>
       <c r="N21" t="n">
-        <v>0.9242</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0583</v>
+        <v>-0.6558</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.8276</v>
+        <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>-3.2353</v>
+        <v>-1.6716</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.822</v>
+        <v>-0.2379</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.4134</v>
+        <v>-1.4336</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1213</v>
+        <v>0.074</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1213</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0134</v>
+        <v>-3.5484</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.951</v>
+        <v>-3.7275</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0625</v>
+        <v>0.179</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3818</v>
@@ -2170,13 +2170,13 @@
         <v>1.9576</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1629</v>
+        <v>-0.6979</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.548</v>
+        <v>-0.3245</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6149</v>
+        <v>-0.3734</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2512</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7500000000000009</v>
+        <v>4.475400000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1264</v>
+        <v>-3.126399999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>3.876299999999999</v>
+        <v>7.601599999999999</v>
       </c>
       <c r="G23" t="n">
         <v>14.3836</v>
@@ -2248,13 +2248,13 @@
         <v>20.6632</v>
       </c>
       <c r="S23" t="n">
-        <v>-16.3309</v>
+        <v>-12.6059</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1441999999999999</v>
+        <v>-0.1442</v>
       </c>
       <c r="U23" t="n">
-        <v>-16.187</v>
+        <v>-12.4617</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5649</v>
